--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536124_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536124_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. GONZÁLEZ RAMÍREZ</t>
+          <t>W. TSAFACK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,67 +890,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.615</v>
+        <v>-0.1713</v>
       </c>
       <c r="E6" t="n">
-        <v>0.615</v>
+        <v>0.594</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.7654</v>
       </c>
       <c r="G6" t="n">
-        <v>0.615</v>
+        <v>-0.2747</v>
       </c>
       <c r="H6" t="n">
-        <v>0.615</v>
+        <v>0.0832</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.3579</v>
       </c>
       <c r="J6" t="n">
-        <v>0.615</v>
+        <v>1.4968</v>
       </c>
       <c r="K6" t="n">
-        <v>0.615</v>
+        <v>1.4563</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.7715</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.3731</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.3984</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.585</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3649</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.0198</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.1585</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.8613</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3315</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. LOPEZ RIAÑO</t>
+          <t>R. ROTCENKOVS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3075</v>
+        <v>-0.9669</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3075</v>
+        <v>-1.0927</v>
       </c>
       <c r="F7" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.1395</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.3075</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.3075</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.3075</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.3075</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.0034</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.1395</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.1361</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.1178</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.2022</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3315</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3315</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. TSAFACK</t>
+          <t>H. SANTA CRUZ CARDENAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1713</v>
+        <v>-1.1714</v>
       </c>
       <c r="E8" t="n">
-        <v>0.594</v>
+        <v>-1.3832</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7654</v>
+        <v>0.2118</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2747</v>
+        <v>-1.4545</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0832</v>
+        <v>-3.0308</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3579</v>
+        <v>1.5763</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4968</v>
+        <v>-0.2865</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4563</v>
+        <v>-1.5905</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>1.3041</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7715</v>
+        <v>-1.1681</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3731</v>
+        <v>-1.4403</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3984</v>
+        <v>0.2722</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.585</v>
+        <v>0.195</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9499</v>
+        <v>-0.9749</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3649</v>
+        <v>1.1699</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0198</v>
+        <v>-0.1904</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1585</v>
+        <v>-0.4004</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8613</v>
+        <v>0.21</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3315</v>
+        <v>0.2786</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.2786</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2201</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. ROTCENKOVS</t>
+          <t>B. GONZALEZ RAMIREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9669</v>
+        <v>-1.22</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0927</v>
+        <v>-2.3328</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1258</v>
+        <v>1.1128</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0034</v>
+        <v>-2.6783</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1395</v>
+        <v>-2.205</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1361</v>
+        <v>-0.4733</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-1.307</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.5615</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0034</v>
+        <v>-1.3714</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1395</v>
+        <v>-1.6436</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1361</v>
+        <v>0.2722</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9749</v>
+        <v>0.585</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5599</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.32</v>
+        <v>0.2104</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1178</v>
+        <v>-0.0509</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2022</v>
+        <v>0.2614</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3315</v>
+        <v>0.6629</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3315</v>
+        <v>0.6629</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. SANTA CRUZ CARDENAL</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1714</v>
+        <v>-1.4167</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3832</v>
+        <v>-3.1979</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2118</v>
+        <v>1.7811</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4545</v>
+        <v>-3.6269</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.0308</v>
+        <v>-0.5177</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5763</v>
+        <v>-3.1092</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2865</v>
+        <v>-2.1274</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5905</v>
+        <v>0.5866</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3041</v>
+        <v>-2.7141</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1681</v>
+        <v>-1.4994</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4403</v>
+        <v>-1.1043</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2722</v>
+        <v>-0.3951</v>
       </c>
       <c r="P10" t="n">
-        <v>0.195</v>
+        <v>2.1448</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1699</v>
+        <v>3.1198</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1904</v>
+        <v>0.3439</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4004</v>
+        <v>-0.3741</v>
       </c>
       <c r="U10" t="n">
-        <v>0.21</v>
+        <v>0.7179</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2786</v>
+        <v>-0.2786</v>
       </c>
       <c r="W10" t="n">
         <v>0.2786</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5571</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4167</v>
+        <v>-2.4212</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1979</v>
+        <v>-1.8313</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7811</v>
+        <v>-0.5899</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6269</v>
+        <v>-1.5576</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5177</v>
+        <v>-0.5125</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.1092</v>
+        <v>-1.045</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1274</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5866</v>
+        <v>0.4471</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.7141</v>
+        <v>-1.3205</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4994</v>
+        <v>-0.6841</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1043</v>
+        <v>-0.9596</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3951</v>
+        <v>0.2755</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1448</v>
+        <v>0.585</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R11" t="n">
-        <v>3.1198</v>
+        <v>1.5599</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3439</v>
+        <v>0.3815</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3741</v>
+        <v>0.0171</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7179</v>
+        <v>0.3644</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2786</v>
+        <v>-1.8301</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2786</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5571</v>
+        <v>-1.8301</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. GONZALEZ RAMIREZ</t>
+          <t>K. EZEAGU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,67 +1388,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.835</v>
+        <v>-2.6316</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9479</v>
+        <v>-3.136</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1128</v>
+        <v>0.5044</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2934</v>
+        <v>-0.1173</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8201</v>
+        <v>-0.0655</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4733</v>
+        <v>-0.0518</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.922</v>
+        <v>0.2946</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1765</v>
+        <v>0.2136</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7455000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3714</v>
+        <v>-0.4119</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6436</v>
+        <v>-0.2791</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2722</v>
+        <v>-0.1328</v>
       </c>
       <c r="P12" t="n">
-        <v>0.585</v>
+        <v>-2.1448</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9749</v>
+        <v>-2.9248</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5599</v>
+        <v>0.7799</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2104</v>
+        <v>0.2934</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0509</v>
+        <v>0.1571</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2614</v>
+        <v>0.1363</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6629</v>
+        <v>-0.6629</v>
       </c>
       <c r="W12" t="n">
+        <v>-0.6629</v>
+      </c>
+      <c r="X12" t="n">
         <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.6629</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>D. LOPEZ RIANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,67 +1471,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4212</v>
+        <v>-3.8718</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8313</v>
+        <v>-2.4578</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5899</v>
+        <v>-1.4139</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5576</v>
+        <v>-2.1845</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5125</v>
+        <v>-0.8833</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.045</v>
+        <v>-1.3012</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4471</v>
+        <v>0.6276</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3205</v>
+        <v>-1.3045</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6841</v>
+        <v>-1.5076</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9596</v>
+        <v>-1.5109</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2755</v>
+        <v>0.0033</v>
       </c>
       <c r="P13" t="n">
-        <v>0.585</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9749</v>
+        <v>-1.9499</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5599</v>
+        <v>1.1699</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3815</v>
+        <v>0.3127</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0171</v>
+        <v>0.1689</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3644</v>
+        <v>0.1438</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8301</v>
+        <v>-1.2201</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8301</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. EZEAGU</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1554,150 +1554,146 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.6316</v>
+        <v>-6.8564</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.136</v>
+        <v>-7.545600000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5044</v>
+        <v>0.6891000000000003</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1173</v>
+        <v>-10.2751</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0655</v>
+        <v>-6.8394</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0518</v>
+        <v>-3.4355</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2946</v>
+        <v>4.0788</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2136</v>
+        <v>6.2192</v>
       </c>
       <c r="L14" t="n">
-        <v>0.081</v>
+        <v>-2.1403</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4119</v>
+        <v>-14.354</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2791</v>
+        <v>-13.0588</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1328</v>
+        <v>-1.295</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.1448</v>
+        <v>-0.9747999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9248</v>
+        <v>-17.5487</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7799</v>
+        <v>16.5738</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2934</v>
+        <v>2.5634</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1571</v>
+        <v>-0.5747</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1363</v>
+        <v>3.138</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6629</v>
+        <v>1.83</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6629</v>
+        <v>6.498899999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>play_by_play_2536124_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-4.668799999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. LOPEZ RIANO</t>
+          <t>A. ANABITARTE SOROA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SPANISH BASKETBALL ACADEMY</t>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.1793</v>
+        <v>5.2179</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.7654</v>
+        <v>2.9707</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4139</v>
+        <v>2.2471</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.492</v>
+        <v>1.8515</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1908</v>
+        <v>2.0667</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3012</v>
+        <v>-0.2152</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9844000000000001</v>
+        <v>2.7308</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3201</v>
+        <v>2.6903</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3045</v>
+        <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5076</v>
+        <v>-0.8794</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5109</v>
+        <v>-0.6236</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0033</v>
+        <v>-0.2557</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7799</v>
+        <v>1.5599</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9499</v>
+        <v>-0.9749</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1699</v>
+        <v>2.5348</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3127</v>
+        <v>0.5336</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1689</v>
+        <v>-0.2838</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1438</v>
+        <v>0.8174</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2201</v>
+        <v>1.273</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.4986</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2201</v>
+        <v>-0.2256</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1708,86 +1704,90 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>Z. VYTAUTAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SPANISH BASKETBALL ACADEMY</t>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.856400000000001</v>
+        <v>4.4906</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.545800000000002</v>
+        <v>4.2534</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6891000000000003</v>
+        <v>0.2373</v>
       </c>
       <c r="G16" t="n">
-        <v>-10.2752</v>
+        <v>1.9549</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.839500000000001</v>
+        <v>1.2192</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.4355</v>
+        <v>0.7356</v>
       </c>
       <c r="J16" t="n">
-        <v>4.0788</v>
+        <v>3.5148</v>
       </c>
       <c r="K16" t="n">
-        <v>6.219200000000001</v>
+        <v>2.2512</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.1403</v>
+        <v>1.2636</v>
       </c>
       <c r="M16" t="n">
-        <v>-14.354</v>
+        <v>-1.5599</v>
       </c>
       <c r="N16" t="n">
-        <v>-13.0588</v>
+        <v>-1.032</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.295</v>
+        <v>-0.5279</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9747999999999999</v>
+        <v>2.5348</v>
       </c>
       <c r="Q16" t="n">
-        <v>-17.5487</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>16.5738</v>
+        <v>2.5348</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5634</v>
+        <v>0.001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5747</v>
+        <v>-0.4814</v>
       </c>
       <c r="U16" t="n">
-        <v>3.138</v>
+        <v>0.4824</v>
       </c>
       <c r="V16" t="n">
-        <v>1.830000000000001</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>6.498899999999999</v>
+        <v>1.2201</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.668799999999999</v>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+        <v>-1.2201</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2536124_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ANABITARTE SOROA</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.2179</v>
+        <v>3.8764</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9707</v>
+        <v>2.4082</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2471</v>
+        <v>1.4682</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8515</v>
+        <v>2.2995</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0667</v>
+        <v>0.783</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2152</v>
+        <v>1.5164</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7308</v>
+        <v>1.7586</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6903</v>
+        <v>1.0621</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>0.6965</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8794</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6236</v>
+        <v>-0.2791</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2557</v>
+        <v>0.8199</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5599</v>
+        <v>0.9749</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5348</v>
+        <v>0.9749</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5336</v>
+        <v>-0.618</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2838</v>
+        <v>-0.5705</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8174</v>
+        <v>-0.0475</v>
       </c>
       <c r="V17" t="n">
-        <v>1.273</v>
+        <v>1.2201</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4986</v>
+        <v>1.2201</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2256</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Z. VYTAUTAS</t>
+          <t>C. SIMMONS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,64 +1882,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.4906</v>
+        <v>1.1263</v>
       </c>
       <c r="E18" t="n">
-        <v>4.2534</v>
+        <v>1.4326</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2373</v>
+        <v>-0.3063</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9549</v>
+        <v>1.8449</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2192</v>
+        <v>1.8708</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7356</v>
+        <v>-0.0259</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5148</v>
+        <v>3.0654</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2512</v>
+        <v>2.5634</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2636</v>
+        <v>0.502</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5599</v>
+        <v>-1.2205</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.032</v>
+        <v>-0.6926</v>
       </c>
       <c r="O18" t="n">
         <v>-0.5279</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5348</v>
+        <v>0.195</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5348</v>
+        <v>2.1448</v>
       </c>
       <c r="S18" t="n">
-        <v>0.001</v>
+        <v>-0.3036</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4814</v>
+        <v>-0.293</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4824</v>
+        <v>-0.0106</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2201</v>
+        <v>0.61</v>
       </c>
       <c r="X18" t="n">
         <v>-1.2201</v>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.8764</v>
+        <v>0.4466</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4082</v>
+        <v>-0.1556</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4682</v>
+        <v>0.6022</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2995</v>
+        <v>1.1747</v>
       </c>
       <c r="H19" t="n">
-        <v>0.783</v>
+        <v>0.4829</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5164</v>
+        <v>0.6918</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7586</v>
+        <v>1.1111</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0621</v>
+        <v>1.1031</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6965</v>
+        <v>0.008</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.0636</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2791</v>
+        <v>-0.6202</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8199</v>
+        <v>0.6838</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9749</v>
+        <v>-0.39</v>
       </c>
       <c r="Q19" t="n">
+        <v>-0.9749</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.0596</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.2918</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.2322</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.2786</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>0.9749</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-0.618</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-0.5705</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.0475</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.2201</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.2201</v>
-      </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. SIMMONS</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1263</v>
+        <v>0.0885</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4326</v>
+        <v>-2.3712</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3063</v>
+        <v>2.4597</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8449</v>
+        <v>0.1821</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8708</v>
+        <v>-0.8144</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0259</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>3.0654</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5634</v>
+        <v>-0.6025</v>
       </c>
       <c r="L20" t="n">
-        <v>0.502</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2205</v>
+        <v>0.7441</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6926</v>
+        <v>-0.2119</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5279</v>
+        <v>0.956</v>
       </c>
       <c r="P20" t="n">
-        <v>0.195</v>
+        <v>-0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9499</v>
+        <v>-0.9749</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1448</v>
+        <v>0.9749</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3036</v>
+        <v>-0.0936</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.293</v>
+        <v>-0.1713</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0106</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.61</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.61</v>
+        <v>-0.6629</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2201</v>
+        <v>0.6629</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>O. SIQUIER COSTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,58 +2131,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4466</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1556</v>
+        <v>-0.0487</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6022</v>
+        <v>-0.0474</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1747</v>
+        <v>-0.0999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4829</v>
+        <v>-0.9505</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6918</v>
+        <v>0.8505</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1111</v>
+        <v>0.243</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1031</v>
+        <v>-0.332</v>
       </c>
       <c r="L21" t="n">
-        <v>0.008</v>
+        <v>0.575</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0636</v>
+        <v>-0.343</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6202</v>
+        <v>-0.6185</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6838</v>
+        <v>0.2755</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.39</v>
+        <v>0.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.585</v>
+        <v>0.39</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0596</v>
+        <v>-0.1076</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2918</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2322</v>
+        <v>0.1841</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2786</v>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0885</v>
+        <v>-0.1555</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3712</v>
+        <v>-0.1535</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4597</v>
+        <v>-0.0019</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1821</v>
+        <v>0.623</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8144</v>
+        <v>0.2147</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.4083</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5620000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6025</v>
+        <v>0.082</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7441</v>
+        <v>0.541</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2119</v>
+        <v>0.1327</v>
       </c>
       <c r="O22" t="n">
-        <v>0.956</v>
+        <v>0.4083</v>
       </c>
       <c r="P22" t="n">
-        <v>-0</v>
+        <v>0.7799</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9749</v>
+        <v>0.7799</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0936</v>
+        <v>-0.3383</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1713</v>
+        <v>-0.2355</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07770000000000001</v>
+        <v>-0.1028</v>
       </c>
       <c r="V22" t="n">
+        <v>-1.2201</v>
+      </c>
+      <c r="W22" t="n">
         <v>0</v>
       </c>
-      <c r="W22" t="n">
-        <v>-0.6629</v>
-      </c>
       <c r="X22" t="n">
-        <v>0.6629</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. SIQUIER COSTA</t>
+          <t>A. GRELA ROJAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-1.9642</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0487</v>
+        <v>-2.6398</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0474</v>
+        <v>0.6757</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0999</v>
+        <v>-1.0131</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9505</v>
+        <v>0.7398</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8505</v>
+        <v>-1.7529</v>
       </c>
       <c r="J23" t="n">
-        <v>0.243</v>
+        <v>-0.2043</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.332</v>
+        <v>1.1567</v>
       </c>
       <c r="L23" t="n">
-        <v>0.575</v>
+        <v>-1.361</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.343</v>
+        <v>-0.8088</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6185</v>
+        <v>-0.4169</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2755</v>
+        <v>-0.3918</v>
       </c>
       <c r="P23" t="n">
-        <v>0.39</v>
+        <v>1.3649</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R23" t="n">
-        <v>0.39</v>
+        <v>2.3398</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1076</v>
+        <v>0.23</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2918</v>
+        <v>-0.1347</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1841</v>
+        <v>0.3646</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2786</v>
+        <v>-2.546</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-1.3259</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2786</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>W. BURGOS MEJIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1555</v>
+        <v>-2.3625</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1535</v>
+        <v>-4.2182</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0019</v>
+        <v>1.8557</v>
       </c>
       <c r="G24" t="n">
-        <v>0.623</v>
+        <v>2.9974</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2147</v>
+        <v>3.028</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4083</v>
+        <v>-0.0306</v>
       </c>
       <c r="J24" t="n">
-        <v>0.082</v>
+        <v>4.149</v>
       </c>
       <c r="K24" t="n">
-        <v>0.082</v>
+        <v>4.06</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="M24" t="n">
-        <v>0.541</v>
+        <v>-1.1516</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1327</v>
+        <v>-1.032</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4083</v>
+        <v>-0.1196</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7799</v>
+        <v>-5.6546</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-8.7743</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7799</v>
+        <v>3.1198</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3383</v>
+        <v>-0.3154</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2355</v>
+        <v>-0.4814</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1028</v>
+        <v>0.166</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2201</v>
+        <v>0.61</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2201</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. GRELA ROJAS</t>
+          <t>R. BAKA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,64 +2463,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9642</v>
+        <v>-2.4981</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6398</v>
+        <v>-2.1229</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6757</v>
+        <v>-0.3752</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.0131</v>
+        <v>-1.5398</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7398</v>
+        <v>-1.8007</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7529</v>
+        <v>0.2609</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2043</v>
+        <v>-1.5345</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1567</v>
+        <v>-0.9755</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.361</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8088</v>
+        <v>-0.0053</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4169</v>
+        <v>-0.8252</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3918</v>
+        <v>0.8199</v>
       </c>
       <c r="P25" t="n">
-        <v>1.3649</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9749</v>
+        <v>-1.9499</v>
       </c>
       <c r="R25" t="n">
-        <v>2.3398</v>
+        <v>1.1699</v>
       </c>
       <c r="S25" t="n">
-        <v>0.23</v>
+        <v>-0.1783</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1347</v>
+        <v>0.1414</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3646</v>
+        <v>-0.3197</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.546</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.3259</v>
+        <v>1.2201</v>
       </c>
       <c r="X25" t="n">
         <v>-1.2201</v>
@@ -2534,7 +2534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>W. BURGOS MEJIA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2546,235 +2546,69 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.3625</v>
+        <v>8.169800000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.2182</v>
+        <v>-0.6450000000000018</v>
       </c>
       <c r="F26" t="n">
-        <v>1.8557</v>
+        <v>8.815100000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9974</v>
+        <v>10.2752</v>
       </c>
       <c r="H26" t="n">
-        <v>3.028</v>
+        <v>6.8395</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0306</v>
+        <v>3.4354</v>
       </c>
       <c r="J26" t="n">
-        <v>4.149</v>
+        <v>14.3539</v>
       </c>
       <c r="K26" t="n">
-        <v>4.06</v>
+        <v>13.0588</v>
       </c>
       <c r="L26" t="n">
-        <v>0.089</v>
+        <v>1.2951</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.1516</v>
+        <v>-4.079000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.032</v>
+        <v>-6.2193</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1196</v>
+        <v>2.1405</v>
       </c>
       <c r="P26" t="n">
-        <v>-5.6546</v>
+        <v>0.9749000000000012</v>
       </c>
       <c r="Q26" t="n">
-        <v>-8.7743</v>
+        <v>-16.5737</v>
       </c>
       <c r="R26" t="n">
-        <v>3.1198</v>
+        <v>17.5486</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3154</v>
+        <v>-1.2498</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4814</v>
+        <v>-3.093799999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>0.166</v>
+        <v>1.8438</v>
       </c>
       <c r="V26" t="n">
-        <v>0.61</v>
+        <v>-1.8302</v>
       </c>
       <c r="W26" t="n">
-        <v>0.8885999999999999</v>
+        <v>4.668699999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.2786</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>play_by_play_2536124_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>R. BAKA</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-2.4981</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-2.1229</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-0.3752</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-1.5398</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-1.8007</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.2609</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-1.5345</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-0.9755</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-0.5590000000000001</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-0.0053</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-0.8252</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0.8199</v>
-      </c>
-      <c r="P27" t="n">
-        <v>-0.7799</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-1.9499</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.1699</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-0.1783</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.1414</v>
-      </c>
-      <c r="U27" t="n">
-        <v>-0.3197</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.2201</v>
-      </c>
-      <c r="X27" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>play_by_play_2536124_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>8.169800000000002</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-0.6450000000000018</v>
-      </c>
-      <c r="F28" t="n">
-        <v>8.815100000000001</v>
-      </c>
-      <c r="G28" t="n">
-        <v>10.2752</v>
-      </c>
-      <c r="H28" t="n">
-        <v>6.8395</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3.4354</v>
-      </c>
-      <c r="J28" t="n">
-        <v>14.3539</v>
-      </c>
-      <c r="K28" t="n">
-        <v>13.0588</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.2951</v>
-      </c>
-      <c r="M28" t="n">
-        <v>-4.079000000000001</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-6.2193</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.1405</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0.9749000000000012</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-16.5737</v>
-      </c>
-      <c r="R28" t="n">
-        <v>17.5486</v>
-      </c>
-      <c r="S28" t="n">
-        <v>-1.2498</v>
-      </c>
-      <c r="T28" t="n">
-        <v>-3.093799999999999</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.8438</v>
-      </c>
-      <c r="V28" t="n">
-        <v>-1.8302</v>
-      </c>
-      <c r="W28" t="n">
-        <v>4.668699999999999</v>
-      </c>
-      <c r="X28" t="n">
         <v>-6.498999999999999</v>
       </c>
-      <c r="Y28" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
